--- a/Modelscore_log.xlsx
+++ b/Modelscore_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurenzpfleiderer/code/xucenying/grid-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52430E2-A9F2-A84C-A044-DC3ECA62BC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F56D4A0-20D0-B94E-BA61-B7EC5F28A2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2980" yWindow="960" windowWidth="28040" windowHeight="17180" activeTab="2" xr2:uid="{C3A6137E-9639-7345-AD33-049E742AC83E}"/>
+    <workbookView xWindow="-32760" yWindow="2540" windowWidth="28040" windowHeight="17180" activeTab="2" xr2:uid="{C3A6137E-9639-7345-AD33-049E742AC83E}"/>
   </bookViews>
   <sheets>
     <sheet name="Covariate log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="64">
   <si>
     <t>price</t>
   </si>
@@ -206,6 +206,30 @@
   </si>
   <si>
     <t>End date</t>
+  </si>
+  <si>
+    <t>{'subsample': 0.7, 'reg_lambda': None, 'reg_alpha': None, 'n_estimators': 800, 'max_depth': 7, 'learning_rate': 0.02, 'gamma': None, 'colsample_bytree': 0.9}</t>
+  </si>
+  <si>
+    <t>Probably overfitting, as I have no regularization!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{'subsample': 0.9, 'reg_lambda': 5, 'reg_alpha': 1, 'n_estimators': 300, 'max_depth': 6, 'learning_rate': 0.01, 'gamma': 0.3, 'colsample_bytree': 0.7} </t>
+  </si>
+  <si>
+    <t>random gs</t>
+  </si>
+  <si>
+    <t>gs</t>
+  </si>
+  <si>
+    <t>prediction</t>
+  </si>
+  <si>
+    <t>prediciton</t>
+  </si>
+  <si>
+    <t>Confirms overfitting hypothesis</t>
   </si>
 </sst>
 </file>
@@ -398,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -463,6 +487,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2367,8 +2394,10 @@
       <c r="AR31" s="33"/>
       <c r="AS31" s="33"/>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="33"/>
+      <c r="B32" s="43"/>
+      <c r="Z32"/>
       <c r="AA32" s="33"/>
       <c r="AB32" s="33"/>
       <c r="AC32" s="33"/>
@@ -2391,16 +2420,10 @@
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A33" s="33"/>
-      <c r="B33" s="34" t="s">
-        <v>43</v>
-      </c>
+      <c r="B33" s="38"/>
       <c r="C33" s="33"/>
-      <c r="D33" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>45</v>
-      </c>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
       <c r="F33" s="33"/>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
@@ -2443,11 +2466,16 @@
       <c r="AS33" s="33"/>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
+      <c r="B34" s="37" t="s">
+        <v>47</v>
+      </c>
       <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
+      <c r="D34" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="35">
+        <v>45689</v>
+      </c>
       <c r="F34" s="33"/>
       <c r="G34" s="33"/>
       <c r="H34" s="33"/>
@@ -2490,11 +2518,14 @@
       <c r="AS34" s="33"/>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="38"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
+      <c r="D35" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="35">
+        <v>46054</v>
+      </c>
       <c r="F35" s="33"/>
       <c r="G35" s="33"/>
       <c r="H35" s="33"/>
@@ -2537,37 +2568,7 @@
       <c r="AS35" s="33"/>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B36" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="35">
-        <v>45689</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
+      <c r="A36" s="33"/>
       <c r="AA36" s="33"/>
       <c r="AB36" s="33"/>
       <c r="AC36" s="33"/>
@@ -2589,13 +2590,16 @@
       <c r="AS36" s="33"/>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B37" s="33"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="34" t="s">
+        <v>43</v>
+      </c>
       <c r="C37" s="33"/>
       <c r="D37" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="35">
-        <v>46054</v>
+        <v>44</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>45</v>
       </c>
       <c r="F37" s="33"/>
       <c r="G37" s="33"/>
@@ -2639,8 +2643,11 @@
       <c r="AS37" s="33"/>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A38" s="33"/>
       <c r="B38" s="33"/>
       <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
       <c r="F38" s="33"/>
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
@@ -2780,7 +2787,9 @@
       <c r="AS40" s="33"/>
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B41" s="33"/>
+      <c r="B41" s="33" t="s">
+        <v>61</v>
+      </c>
       <c r="C41" s="33"/>
       <c r="D41" s="36">
         <v>288</v>
@@ -2830,7 +2839,9 @@
       <c r="AS41" s="33"/>
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B42" s="33"/>
+      <c r="B42" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="C42" s="33"/>
       <c r="D42" s="36" t="s">
         <v>49</v>
@@ -3483,7 +3494,7 @@
     <mergeCell ref="E28:F30"/>
     <mergeCell ref="G28:G30"/>
   </mergeCells>
-  <conditionalFormatting sqref="D31:Y31">
+  <conditionalFormatting sqref="D31:Y32">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -3494,7 +3505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE124B7E-2980-1447-BCD3-5A4CA67A7D50}">
-  <dimension ref="A1:AS55"/>
+  <dimension ref="A1:AS56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="17.5" customWidth="1"/>
@@ -4578,8 +4589,10 @@
       <c r="AR31" s="33"/>
       <c r="AS31" s="33"/>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="33"/>
+      <c r="B32" s="43"/>
+      <c r="Z32"/>
       <c r="AA32" s="33"/>
       <c r="AB32" s="33"/>
       <c r="AC32" s="33"/>
@@ -4600,39 +4613,10 @@
       <c r="AR32" s="33"/>
       <c r="AS32" s="33"/>
     </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:45" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="33"/>
-      <c r="B33" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="33"/>
+      <c r="B33" s="43"/>
+      <c r="Z33"/>
       <c r="AA33" s="33"/>
       <c r="AB33" s="33"/>
       <c r="AC33" s="33"/>
@@ -4654,11 +4638,16 @@
       <c r="AS33" s="33"/>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
+      <c r="B34" s="37" t="s">
+        <v>47</v>
+      </c>
       <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
+      <c r="D34" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="35">
+        <v>45689</v>
+      </c>
       <c r="F34" s="33"/>
       <c r="G34" s="33"/>
       <c r="H34" s="33"/>
@@ -4701,11 +4690,14 @@
       <c r="AS34" s="33"/>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="38"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
+      <c r="D35" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="35">
+        <v>46054</v>
+      </c>
       <c r="F35" s="33"/>
       <c r="G35" s="33"/>
       <c r="H35" s="33"/>
@@ -4748,37 +4740,7 @@
       <c r="AS35" s="33"/>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B36" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="35">
-        <v>45689</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
+      <c r="A36" s="33"/>
       <c r="AA36" s="33"/>
       <c r="AB36" s="33"/>
       <c r="AC36" s="33"/>
@@ -4800,13 +4762,16 @@
       <c r="AS36" s="33"/>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B37" s="33"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="34" t="s">
+        <v>43</v>
+      </c>
       <c r="C37" s="33"/>
       <c r="D37" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="35">
-        <v>46054</v>
+        <v>44</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="F37" s="33"/>
       <c r="G37" s="33"/>
@@ -4850,8 +4815,11 @@
       <c r="AS37" s="33"/>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A38" s="33"/>
       <c r="B38" s="33"/>
       <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
       <c r="F38" s="33"/>
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
@@ -4991,13 +4959,15 @@
       <c r="AS40" s="33"/>
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B41" s="33"/>
+      <c r="B41" s="33" t="s">
+        <v>62</v>
+      </c>
       <c r="C41" s="33"/>
       <c r="D41" s="36">
         <v>288</v>
       </c>
       <c r="E41" s="39">
-        <v>26.08</v>
+        <v>27.06</v>
       </c>
       <c r="F41" s="33"/>
       <c r="G41" s="33"/>
@@ -5041,16 +5011,20 @@
       <c r="AS41" s="33"/>
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B42" s="33"/>
+      <c r="B42" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="C42" s="33"/>
       <c r="D42" s="36" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="40">
-        <v>29.228300000000001</v>
+        <v>9.9052000000000007</v>
       </c>
       <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
+      <c r="G42" s="33" t="s">
+        <v>57</v>
+      </c>
       <c r="H42" s="33"/>
       <c r="I42" s="33"/>
       <c r="J42" s="33"/>
@@ -5093,8 +5067,8 @@
     <row r="43" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="40"/>
       <c r="F43" s="33"/>
       <c r="G43" s="33"/>
       <c r="H43" s="33"/>
@@ -5229,10 +5203,16 @@
       <c r="AS45" s="33"/>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B46" s="33"/>
+      <c r="B46" s="34" t="s">
+        <v>43</v>
+      </c>
       <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
+      <c r="D46" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>58</v>
+      </c>
       <c r="F46" s="33"/>
       <c r="G46" s="33"/>
       <c r="H46" s="33"/>
@@ -5367,9 +5347,13 @@
       <c r="AS48" s="33"/>
     </row>
     <row r="49" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
+      <c r="B49" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="37"/>
+      <c r="D49" s="42" t="s">
+        <v>50</v>
+      </c>
       <c r="E49" s="33"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
@@ -5413,10 +5397,16 @@
       <c r="AS49" s="33"/>
     </row>
     <row r="50" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B50" s="33"/>
+      <c r="B50" s="33" t="s">
+        <v>61</v>
+      </c>
       <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
+      <c r="D50" s="36">
+        <v>288</v>
+      </c>
+      <c r="E50" s="33">
+        <v>25.21</v>
+      </c>
       <c r="F50" s="33"/>
       <c r="G50" s="33"/>
       <c r="H50" s="33"/>
@@ -5459,12 +5449,20 @@
       <c r="AS50" s="33"/>
     </row>
     <row r="51" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B51" s="33"/>
+      <c r="B51" s="33" t="s">
+        <v>59</v>
+      </c>
       <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
+      <c r="D51" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51" s="40">
+        <v>28.154260000000001</v>
+      </c>
       <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
+      <c r="G51" s="33" t="s">
+        <v>63</v>
+      </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
       <c r="J51" s="33"/>
@@ -5688,13 +5686,59 @@
       <c r="AR55" s="33"/>
       <c r="AS55" s="33"/>
     </row>
+    <row r="56" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="33"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="33"/>
+      <c r="AA56" s="33"/>
+      <c r="AB56" s="33"/>
+      <c r="AC56" s="33"/>
+      <c r="AD56" s="33"/>
+      <c r="AE56" s="33"/>
+      <c r="AF56" s="33"/>
+      <c r="AG56" s="33"/>
+      <c r="AH56" s="33"/>
+      <c r="AI56" s="33"/>
+      <c r="AJ56" s="33"/>
+      <c r="AK56" s="33"/>
+      <c r="AL56" s="33"/>
+      <c r="AM56" s="33"/>
+      <c r="AN56" s="33"/>
+      <c r="AO56" s="33"/>
+      <c r="AP56" s="33"/>
+      <c r="AQ56" s="33"/>
+      <c r="AR56" s="33"/>
+      <c r="AS56" s="33"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="E28:F30"/>
     <mergeCell ref="G28:G30"/>
   </mergeCells>
-  <conditionalFormatting sqref="D31:Y31">
+  <conditionalFormatting sqref="D31:Y33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
